--- a/outputs/daily/predictions_2026-06-14.xlsx
+++ b/outputs/daily/predictions_2026-06-14.xlsx
@@ -1385,31 +1385,31 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.470668472855597</v>
+        <v>1.431202569171815</v>
       </c>
       <c r="L4" t="n">
-        <v>1.202566469064705</v>
+        <v>1.192532372748487</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4772619478221033</v>
+        <v>0.4636744058120388</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2677091031652398</v>
+        <v>0.2767254189203314</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2550289490126569</v>
+        <v>0.2596001752676299</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4980764737474084</v>
+        <v>0.4773875024127186</v>
       </c>
       <c r="R4" t="n">
-        <v>1.598341638617162</v>
+        <v>1.526585450101195</v>
       </c>
       <c r="S4" t="n">
-        <v>1.071658361382838</v>
+        <v>1.053414549898805</v>
       </c>
       <c r="T4" t="n">
         <v>0.4497826045516286</v>
@@ -1427,58 +1427,58 @@
         <v>0.5569584607736159</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4211797196022785</v>
+        <v>0.4130269456468246</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2813722060134428</v>
+        <v>0.2850670705740695</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2974480743842789</v>
+        <v>0.301905983779106</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4997961870903878</v>
+        <v>0.4875122930983395</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5002038129096122</v>
+        <v>0.5124877069016605</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.551042673304573</v>
+        <v>0.5424375872861055</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.448957326695427</v>
+        <v>0.4575624127138945</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.420565</v>
+        <v>0.41231</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.28038</v>
+        <v>0.28455</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.299055</v>
+        <v>0.30314</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.499735</v>
+        <v>0.48752</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.55108</v>
+        <v>0.5424</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.469935</v>
+        <v>1.43073</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.206475</v>
+        <v>1.19488</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.67641</v>
+        <v>2.62561</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.4536236206224809</v>
+        <v>0.4461504103295917</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.253426128138924</v>
+        <v>0.2579563705811173</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2929502512385951</v>
+        <v>0.2958932190892911</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.4536236206224809</v>
+        <v>0.4461504103295917</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>3.921123479791194</v>
+        <v>3.852077522555866</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2929502512385951</v>
+        <v>0.2958932190892911</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0379213022259382</v>
+        <v>0.03629304382166126</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1486941085423843</v>
+        <v>0.1398036183305564</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3.921123479791194</v>
+        <v>3.852077522555866</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.2929502512385951</v>
+        <v>0.2958932190892911</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0379213022259382</v>
+        <v>0.03629304382166126</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1486941085423843</v>
+        <v>0.1398036183305564</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -1531,23 +1531,23 @@
         </is>
       </c>
       <c r="BE4" t="n">
-        <v>0.1342905954296841</v>
+        <v>0.1361728540615039</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.09142789756900938</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BG4" t="n">
-        <v>0.0897713385906556</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
       <c r="BI4" t="n">
-        <v>0.08930994422901455</v>
+        <v>0.08858679026558318</v>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>0.08123683216198897</v>
+        <v>0.08491083555116558</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
@@ -1563,23 +1563,23 @@
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>0.07464979350411724</v>
+        <v>0.07428459997393021</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.07411679375376053</v>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="BO4" t="n">
-        <v>0.07340607598839637</v>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="BQ4" t="n">
-        <v>0.07080323926521276</v>
+        <v>0.07381388034449937</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="BS4" t="n">
-        <v>0.05397800083608839</v>
+        <v>0.05282130759479424</v>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="BU4" t="n">
-        <v>0.04991340831959482</v>
+        <v>0.05157472599229108</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.04400795914377407</v>
+        <v>0.04226188060759579</v>
       </c>
     </row>
     <row r="5">
@@ -1656,31 +1656,31 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9294785184646961</v>
+        <v>0.9583184500244093</v>
       </c>
       <c r="L5" t="n">
-        <v>1.175641727972558</v>
+        <v>1.146801796412845</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.263902604399794</v>
+        <v>0.2915523506567922</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3374469089297338</v>
+        <v>0.3347318033397587</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3986504866704723</v>
+        <v>0.373715846003449</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3294174684866114</v>
+        <v>0.3279117252181696</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8764831756081588</v>
+        <v>0.9289194148076373</v>
       </c>
       <c r="S5" t="n">
-        <v>1.143516824391841</v>
+        <v>1.091080585192363</v>
       </c>
       <c r="T5" t="n">
         <v>0.3307563414801561</v>
@@ -1698,58 +1698,58 @@
         <v>0.4356262604828165</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.275724998447915</v>
+        <v>0.2897040128585189</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3226851385713614</v>
+        <v>0.3241036278124453</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.4015898629807236</v>
+        <v>0.3861923593290358</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3517509914576831</v>
+        <v>0.3517509975331365</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6482490085423169</v>
+        <v>0.6482490024668635</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4317635185082283</v>
+        <v>0.4340319199063341</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5682364814917717</v>
+        <v>0.5659680800936659</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.27637</v>
+        <v>0.289865</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.32273</v>
+        <v>0.324325</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.4009</v>
+        <v>0.38581</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.35003</v>
+        <v>0.350745</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.431165</v>
+        <v>0.43348</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.93057</v>
+        <v>0.959125</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.171745</v>
+        <v>1.144145</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.102315</v>
+        <v>2.10327</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.290257010889951</v>
+        <v>0.3048116629954013</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.3266204921345418</v>
+        <v>0.3258890722088227</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.3831224969755072</v>
+        <v>0.369299264795776</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
@@ -1757,44 +1757,44 @@
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.3831224969755072</v>
+        <v>0.369299264795776</v>
       </c>
       <c r="AS5" t="b">
         <v>1</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OVER_2_5</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>3.789276738190389</v>
+        <v>3.049601228302128</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.290257010889951</v>
+        <v>0.3517509975331365</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.02635440649015702</v>
+        <v>0.02383927231496696</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.09986413946196593</v>
+        <v>0.07270027413355207</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OVER_2_5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3.789276738190389</v>
+        <v>3.049601228302128</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.290257010889951</v>
+        <v>0.3517509975331365</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.02635440649015702</v>
+        <v>0.02383927231496696</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.09986413946196593</v>
+        <v>0.07270027413355207</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="BE5" t="n">
-        <v>0.146441764130498</v>
+        <v>0.1472817081867848</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>0.1351439180604276</v>
+        <v>0.1352202754691867</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="BI5" t="n">
-        <v>0.1299167554662495</v>
+        <v>0.1263267970273083</v>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>0.09992643800233234</v>
+        <v>0.1033636769364781</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>0.08419337256399805</v>
+        <v>0.08011330467969703</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="BO5" t="n">
-        <v>0.07825593119533109</v>
+        <v>0.07677405796698052</v>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="BQ5" t="n">
-        <v>0.06187021543880535</v>
+        <v>0.0641558083211395</v>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="BS5" t="n">
-        <v>0.05262676031881162</v>
+        <v>0.05594324016740869</v>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="BU5" t="n">
-        <v>0.03636860349425577</v>
+        <v>0.03678699811650046</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="BW5" t="n">
-        <v>0.032993747334992</v>
+        <v>0.0306246939077487</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/daily/predictions_2026-06-14.xlsx
+++ b/outputs/daily/predictions_2026-06-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW5"/>
+  <dimension ref="A1:BW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1338,12 +1338,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WC2026-010</t>
+          <t>WC2026-009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T20:00:00+00:00</t>
+          <t>2026-06-14T17:00:00+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1373,112 +1373,112 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Curacao</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.431202569171815</v>
+        <v>3.183061343967819</v>
       </c>
       <c r="L4" t="n">
-        <v>1.192532372748487</v>
+        <v>0.7987982870366475</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4636744058120388</v>
+        <v>0.9281741686461311</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2767254189203314</v>
+        <v>0.04835340770067267</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2596001752676299</v>
+        <v>0.02347242365319626</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4773875024127186</v>
+        <v>0.7882375341840909</v>
       </c>
       <c r="R4" t="n">
-        <v>1.526585450101195</v>
+        <v>3.38957469948742</v>
       </c>
       <c r="S4" t="n">
-        <v>1.053414549898805</v>
+        <v>0.8004253005125802</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4497826045516286</v>
+        <v>0.8623856048543814</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2171412439127638</v>
+        <v>0.1084864120029263</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3330761515356075</v>
+        <v>0.02912798314269217</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5078007077739424</v>
+        <v>0.7068542881642401</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5569584607736159</v>
+        <v>0.4123168874131831</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4130269456468246</v>
+        <v>0.8287505522041857</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2850670705740695</v>
+        <v>0.1157744407447381</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.301905983779106</v>
+        <v>0.05547500705107622</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4875122930983395</v>
+        <v>0.759111908769356</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5124877069016605</v>
+        <v>0.240888091230644</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5424375872861055</v>
+        <v>0.5320567507635946</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4575624127138945</v>
+        <v>0.4679432492364054</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.41231</v>
+        <v>0.8276250000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.28455</v>
+        <v>0.116405</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.30314</v>
+        <v>0.05597</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.48752</v>
+        <v>0.759095</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.5424</v>
+        <v>0.53216</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.43073</v>
+        <v>3.17964</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.19488</v>
+        <v>0.80006</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.62561</v>
+        <v>3.9797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.4461504103295917</v>
+        <v>0.8802922672085324</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2579563705811173</v>
+        <v>0.08625521746747779</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2958932190892911</v>
+        <v>0.03345251532398982</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1486,135 +1486,135 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.4461504103295917</v>
+        <v>0.8802922672085324</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>DRAW</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>3.852077522555866</v>
+        <v>20.68106566946446</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2958932190892911</v>
+        <v>0.08625521746747779</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.03629304382166126</v>
+        <v>0.03790180976680513</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1398036183305564</v>
+        <v>0.7838498167788464</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>DRAW</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3.852077522555866</v>
+        <v>20.68106566946446</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.2958932190892911</v>
+        <v>0.08625521746747779</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03629304382166126</v>
+        <v>0.03790180976680513</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1398036183305564</v>
+        <v>0.7838498167788464</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.1002976917966654</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.0945294616958027</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.08011762440090592</v>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.07981342641179094</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.07550997207710357</v>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.06375482830026412</v>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.05465082515794061</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="BE4" t="n">
-        <v>0.1361728540615039</v>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="BG4" t="n">
-        <v>0.09142789756900938</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="BI4" t="n">
-        <v>0.08858679026558318</v>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.08491083555116558</v>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.07428459997393021</v>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.07411679375376053</v>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0.07381388034449937</v>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
       <c r="BS4" t="n">
-        <v>0.05282130759479424</v>
+        <v>0.05218936131546555</v>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="BU4" t="n">
-        <v>0.05157472599229108</v>
+        <v>0.05081020646819839</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.04226188060759579</v>
+        <v>0.04058710589077524</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WC2026-011</t>
+          <t>WC2026-010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-14T23:00:00+00:00</t>
+          <t>2026-06-14T20:00:00+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1644,237 +1644,508 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9583184500244093</v>
+        <v>1.427797298019097</v>
       </c>
       <c r="L5" t="n">
-        <v>1.146801796412845</v>
+        <v>1.190437643901205</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2915523506567922</v>
+        <v>0.4624436423831809</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3347318033397587</v>
+        <v>0.2784603752850197</v>
       </c>
       <c r="P5" t="n">
-        <v>0.373715846003449</v>
+        <v>0.2590959823317994</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3279117252181696</v>
+        <v>0.4731733652849035</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9289194148076373</v>
+        <v>1.520394048005344</v>
       </c>
       <c r="S5" t="n">
-        <v>1.091080585192363</v>
+        <v>1.049605951994655</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3307563414801561</v>
+        <v>0.4497826045516286</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3170584111994513</v>
+        <v>0.2171412439127638</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3521852473203926</v>
+        <v>0.3330761515356075</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3620714023047004</v>
+        <v>0.5078007077739424</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4356262604828165</v>
+        <v>0.5569584607736159</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2897040128585189</v>
+        <v>0.4125871615311323</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3241036278124453</v>
+        <v>0.2854405534113996</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3861923593290358</v>
+        <v>0.3019722850574683</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3517509975331365</v>
+        <v>0.4861383111324579</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6482490024668635</v>
+        <v>0.513861688867542</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4340319199063341</v>
+        <v>0.5414028199032452</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5659680800936659</v>
+        <v>0.4585971800967548</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.289865</v>
+        <v>0.41219</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.324325</v>
+        <v>0.28465</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.38581</v>
+        <v>0.30316</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.350745</v>
+        <v>0.486285</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.43348</v>
+        <v>0.541165</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.959125</v>
+        <v>1.427555</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.144145</v>
+        <v>1.192175</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.10327</v>
+        <v>2.61973</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.3048116629954013</v>
+        <v>0.4455481589291255</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.3258890722088227</v>
+        <v>0.2587437238363252</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.369299264795776</v>
+        <v>0.2957081172345494</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.369299264795776</v>
+        <v>0.4455481589291255</v>
       </c>
       <c r="AS5" t="b">
         <v>1</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.859573548768487</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.2957081172345494</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.03661213490275006</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.1413072274345977</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.859573548768487</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.2957081172345494</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.03661213490275006</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.1413072274345977</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.1363581431510237</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.0917352134398185</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.08849626743360582</v>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.08532770157744156</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.07442421622440269</v>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.07433927168464961</v>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.07378448484520353</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.05267464404885631</v>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.05167714279020624</v>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.04211824384215928</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WC2026-011</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-14T23:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.9558969607721188</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.143723285665135</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2916717217772</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3346870553158481</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.373641222906952</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3253288671307243</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9245167070762</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.0854832929238</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3307563414801561</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3170584111994513</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3521852473203926</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.3620714023047004</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4356262604828165</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.2895764524332448</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.3245893381572342</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.3858342094095209</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.3502660782628037</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6497339217371962</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.432798356730433</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.567201643269567</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.289955</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.324925</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.349065</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.956885</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.14017</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2.097055</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.3048275213372458</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.3259926005854558</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.3691798780772984</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.3691798780772984</v>
+      </c>
+      <c r="AS6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
           <t>OVER_2_5</t>
         </is>
       </c>
-      <c r="AU5" t="n">
-        <v>3.049601228302128</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.3517509975331365</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.02383927231496696</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.07270027413355207</v>
-      </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AU6" t="n">
+        <v>3.073812689355285</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.3502660782628037</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.02493721113207936</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.07665231601491751</v>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>OVER_2_5</t>
         </is>
       </c>
-      <c r="AZ5" t="n">
-        <v>3.049601228302128</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.3517509975331365</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.02383927231496696</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.07270027413355207</v>
-      </c>
-      <c r="BD5" t="inlineStr">
+      <c r="AZ6" t="n">
+        <v>3.073812689355285</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.3502660782628037</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.02493721113207936</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.07665231601491751</v>
+      </c>
+      <c r="BD6" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="BE5" t="n">
-        <v>0.1472817081867848</v>
-      </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BE6" t="n">
+        <v>0.14732324003563</v>
+      </c>
+      <c r="BF6" t="inlineStr">
         <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="BG5" t="n">
-        <v>0.1352202754691867</v>
-      </c>
-      <c r="BH5" t="inlineStr">
+      <c r="BG6" t="n">
+        <v>0.1358959676814354</v>
+      </c>
+      <c r="BH6" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BI5" t="n">
-        <v>0.1263267970273083</v>
-      </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BI6" t="n">
+        <v>0.1267164499212531</v>
+      </c>
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="BK5" t="n">
-        <v>0.1033636769364781</v>
-      </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BK6" t="n">
+        <v>0.1037071718117984</v>
+      </c>
+      <c r="BL6" t="inlineStr">
         <is>
           <t>0-2</t>
         </is>
       </c>
-      <c r="BM5" t="n">
-        <v>0.08011330467969703</v>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BM6" t="n">
+        <v>0.08012323268716874</v>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="BO5" t="n">
-        <v>0.07677405796698052</v>
-      </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BO6" t="n">
+        <v>0.07658955461290189</v>
+      </c>
+      <c r="BP6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BQ5" t="n">
-        <v>0.0641558083211395</v>
-      </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BQ6" t="n">
+        <v>0.06401174427325459</v>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="BS5" t="n">
-        <v>0.05594324016740869</v>
-      </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BS6" t="n">
+        <v>0.05596785959991048</v>
+      </c>
+      <c r="BT6" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
       </c>
-      <c r="BU5" t="n">
-        <v>0.03678699811650046</v>
-      </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BU6" t="n">
+        <v>0.03660586124068157</v>
+      </c>
+      <c r="BV6" t="inlineStr">
         <is>
           <t>0-3</t>
         </is>
       </c>
-      <c r="BW5" t="n">
-        <v>0.0306246939077487</v>
+      <c r="BW6" t="n">
+        <v>0.03054626898236026</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/daily/predictions_2026-06-14.xlsx
+++ b/outputs/daily/predictions_2026-06-14.xlsx
@@ -796,12 +796,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WC2026-007</t>
+          <t>WC2026-008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14T01:00:00+00:00</t>
+          <t>2026-06-14T04:00:00+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -831,112 +831,112 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.107126625504258</v>
+        <v>1.02854252273608</v>
       </c>
       <c r="L2" t="n">
-        <v>1.811086135136016</v>
+        <v>1.447146221056096</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1598824608210085</v>
+        <v>0.1838704212592941</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2135738072388958</v>
+        <v>0.2541015036332722</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6265437319400957</v>
+        <v>0.5620280751074338</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.576876007556346</v>
+        <v>0.4769189468613719</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9214399984013179</v>
+        <v>0.8648949833037775</v>
       </c>
       <c r="S2" t="n">
-        <v>2.078560001598682</v>
+        <v>1.715105016696223</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3348660789315561</v>
+        <v>0.3910937279047658</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2727712559469634</v>
+        <v>0.267082621876318</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3923626651214805</v>
+        <v>0.3418236502189161</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4607623971779005</v>
+        <v>0.4279430465453672</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5341478296809155</v>
+        <v>0.5177335029005276</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2202678109910944</v>
+        <v>0.2558937557988304</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2520840363057984</v>
+        <v>0.289377427903463</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5276481527031069</v>
+        <v>0.4547288162977067</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5582373202181997</v>
+        <v>0.4499354578353799</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4417626797818003</v>
+        <v>0.5500645421646201</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5708796778822048</v>
+        <v>0.503855287705818</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4291203221177952</v>
+        <v>0.496144712294182</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.21996</v>
+        <v>0.25568</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.25104</v>
+        <v>0.28916</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.529</v>
+        <v>0.45516</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.558215</v>
+        <v>0.449415</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.571055</v>
+        <v>0.50449</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.10701</v>
+        <v>1.028535</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.8129</v>
+        <v>1.448255</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.91991</v>
+        <v>2.47679</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.2362230647022216</v>
+        <v>0.2744044122200933</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2439204715534451</v>
+        <v>0.267463876085886</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.5198564637443333</v>
+        <v>0.4581317116940209</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.5198564637443333</v>
+        <v>0.4581317116940209</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>6.254594749573682</v>
+        <v>5.438612655320999</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2362230647022216</v>
+        <v>0.2744044122200933</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.07634060388121308</v>
+        <v>0.0905339909607992</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.4774795402147196</v>
+        <v>0.4923793089761195</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -972,16 +972,16 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>6.254594749573682</v>
+        <v>5.438612655320999</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2362230647022216</v>
+        <v>0.2744044122200933</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.07634060388121308</v>
+        <v>0.0905339909607992</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4774795402147196</v>
+        <v>0.4923793089761195</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -989,90 +989,90 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.1191699717794337</v>
+        <v>0.1377049545522407</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.1091937127152771</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.09662370964325673</v>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="BG2" t="n">
-        <v>0.0981032198246739</v>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BK2" t="n">
+        <v>0.09058145663680754</v>
+      </c>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>0-2</t>
         </is>
       </c>
-      <c r="BI2" t="n">
-        <v>0.08861065894787891</v>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.08701997705867641</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
       <c r="BM2" t="n">
-        <v>0.0648639799856449</v>
+        <v>0.08806778002317985</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.07398701626344291</v>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BO2" t="n">
-        <v>0.05997102214436459</v>
-      </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BQ2" t="n">
+        <v>0.06437972788564496</v>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.04658343996116544</v>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.04448736896722297</v>
+      </c>
+      <c r="BV2" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="BQ2" t="n">
-        <v>0.05922446041222255</v>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.05430634335779684</v>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0-3</t>
-        </is>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.05349384528192322</v>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
       <c r="BW2" t="n">
-        <v>0.04898480105127954</v>
+        <v>0.04369487088990423</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WC2026-008</t>
+          <t>WC2026-009</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T04:00:00+00:00</t>
+          <t>2026-06-14T17:00:00+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1102,248 +1102,248 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Curacao</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1.127144645380598</v>
+        <v>3.233332551496972</v>
       </c>
       <c r="L3" t="n">
-        <v>1.441348104000873</v>
+        <v>0.7955998284672136</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1838704212592941</v>
+        <v>0.9281741686461311</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2541015036332722</v>
+        <v>0.04835340770067267</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5620280751074338</v>
+        <v>0.02347242365319626</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4769189468613719</v>
+        <v>0.7882375341840909</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8648949833037775</v>
+        <v>3.38957469948742</v>
       </c>
       <c r="S3" t="n">
-        <v>1.715105016696223</v>
+        <v>0.8004253005125802</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4225368469848204</v>
+        <v>0.8748245735445831</v>
       </c>
       <c r="U3" t="n">
-        <v>0.280635709677956</v>
+        <v>0.0989414350966443</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2968274433372236</v>
+        <v>0.02623399135877254</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4607259947110685</v>
+        <v>0.650745606643273</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5226349408777385</v>
+        <v>0.3978904069794684</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2829166022923097</v>
+        <v>0.8347171711870884</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2867815372052306</v>
+        <v>0.1121333559707798</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4303018605024596</v>
+        <v>0.0531494728421318</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.47363204727626</v>
+        <v>0.7659788562849787</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.52636795272374</v>
+        <v>0.2340211437150213</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5285381875212246</v>
+        <v>0.5316249727045305</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4714618124787754</v>
+        <v>0.4683750272954695</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.282285</v>
+        <v>0.834735</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.285875</v>
+        <v>0.1121</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.43184</v>
+        <v>0.053165</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.473375</v>
+        <v>0.76602</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.529295</v>
+        <v>0.531305</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.12689</v>
+        <v>3.22988</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.44298</v>
+        <v>0.794395</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.56987</v>
+        <v>4.024275</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.2921652155214822</v>
+        <v>0.8861375609958286</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2715584841419011</v>
+        <v>0.08200420435678954</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4362763003366167</v>
+        <v>0.03185823464738184</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.4362763003366167</v>
+        <v>0.8861375609958286</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>DRAW</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>5.438612655320999</v>
+        <v>20.68106566946446</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2921652155214822</v>
+        <v>0.08200420435678954</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1082947942621882</v>
+        <v>0.03365079665611688</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.5889734385797205</v>
+        <v>0.6959343354749483</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>DRAW</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>5.438612655320999</v>
+        <v>20.68106566946446</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2921652155214822</v>
+        <v>0.08200420435678954</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1082947942621882</v>
+        <v>0.03365079665611688</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.5889734385797205</v>
+        <v>0.6959343354749483</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.1002978728861153</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.09305990456163804</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.08107409431214554</v>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.0797969704638197</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.07403844410641447</v>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.06450253552787769</v>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.05298314280189919</v>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.05242790164451914</v>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="BE3" t="n">
-        <v>0.1369806327890337</v>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="BG3" t="n">
-        <v>0.09802802039346788</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="BI3" t="n">
-        <v>0.08974398879786978</v>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.0891038067733616</v>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.0796206495463289</v>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.07394400418234572</v>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0.07018044853136604</v>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="BS3" t="n">
-        <v>0.05057722821430766</v>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
       <c r="BU3" t="n">
-        <v>0.04869083903920238</v>
+        <v>0.05037668549085659</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.04311744269976175</v>
+        <v>0.04171162955527537</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WC2026-009</t>
+          <t>WC2026-010</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T17:00:00+00:00</t>
+          <t>2026-06-14T20:00:00+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1373,112 +1373,112 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.183061343967819</v>
+        <v>1.477997979411952</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7987982870366475</v>
+        <v>1.160402399130864</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9281741686461311</v>
+        <v>0.4624436423831809</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04835340770067267</v>
+        <v>0.2784603752850197</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02347242365319626</v>
+        <v>0.2590959823317994</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7882375341840909</v>
+        <v>0.4731733652849035</v>
       </c>
       <c r="R4" t="n">
-        <v>3.38957469948742</v>
+        <v>1.520394048005344</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8004253005125802</v>
+        <v>1.049605951994655</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8623856048543814</v>
+        <v>0.3205856946994724</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1084864120029263</v>
+        <v>0.282549883360464</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02912798314269217</v>
+        <v>0.3968644219400635</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7068542881642401</v>
+        <v>0.5607133710451008</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4123168874131831</v>
+        <v>0.5455471673368566</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8287505522041857</v>
+        <v>0.4324644726445199</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1157744407447381</v>
+        <v>0.2823064276068533</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05547500705107622</v>
+        <v>0.2852290997486268</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.759111908769356</v>
+        <v>0.4911670899677775</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.240888091230644</v>
+        <v>0.5088329100322225</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5320567507635946</v>
+        <v>0.5422800604835046</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4679432492364054</v>
+        <v>0.4577199395164954</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.8276250000000001</v>
+        <v>0.431755</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.116405</v>
+        <v>0.28164</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.05597</v>
+        <v>0.286605</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.759095</v>
+        <v>0.490815</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.53216</v>
+        <v>0.54222</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.17964</v>
+        <v>1.4772</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.80006</v>
+        <v>1.164275</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.9797</v>
+        <v>2.641475</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.8802922672085324</v>
+        <v>0.4052985682592177</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08625521746747779</v>
+        <v>0.2808532161918836</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.03345251532398982</v>
+        <v>0.3138482155488987</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1486,135 +1486,135 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.8802922672085324</v>
+        <v>0.4052985682592177</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>20.68106566946446</v>
+        <v>3.859573548768487</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.08625521746747779</v>
+        <v>0.3138482155488987</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.03790180976680513</v>
+        <v>0.05475223321709932</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.7838498167788464</v>
+        <v>0.2113202710607198</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>20.68106566946446</v>
+        <v>3.859573548768487</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.08625521746747779</v>
+        <v>0.3138482155488987</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03790180976680513</v>
+        <v>0.05475223321709932</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.7838498167788464</v>
+        <v>0.2113202710607198</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="BE4" t="n">
-        <v>0.1002976917966654</v>
+        <v>0.1348443161757001</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.09338214325481457</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.09059073947403236</v>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.0837341235044527</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="BG4" t="n">
-        <v>0.0945294616958027</v>
-      </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BM4" t="n">
+        <v>0.07806838346928993</v>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.07112439454520146</v>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.07068182469685581</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.05256085571235312</v>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.04812211893110948</v>
+      </c>
+      <c r="BV4" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="BI4" t="n">
-        <v>0.08011762440090592</v>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>4-0</t>
-        </is>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.07981342641179094</v>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.07550997207710357</v>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>4-1</t>
-        </is>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.06375482830026412</v>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0.05465082515794061</v>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.05218936131546555</v>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>5-0</t>
-        </is>
-      </c>
-      <c r="BU4" t="n">
-        <v>0.05081020646819839</v>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>5-1</t>
-        </is>
-      </c>
       <c r="BW4" t="n">
-        <v>0.04058710589077524</v>
+        <v>0.04463097663201813</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WC2026-010</t>
+          <t>WC2026-011</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-14T20:00:00+00:00</t>
+          <t>2026-06-14T23:00:00+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1644,248 +1644,212 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.427797298019097</v>
+        <v>0.9260431553019546</v>
       </c>
       <c r="L5" t="n">
-        <v>1.190437643901205</v>
+        <v>1.291561593338909</v>
       </c>
       <c r="M5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.4624436423831809</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.2784603752850197</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.2590959823317994</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.4731733652849035</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.520394048005344</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.049605951994655</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>0.4497826045516286</v>
+        <v>0.3275646476432579</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2171412439127638</v>
+        <v>0.32747592871209</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3330761515356075</v>
+        <v>0.3449594236446522</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5078007077739424</v>
+        <v>0.3669194412690598</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5569584607736159</v>
+        <v>0.4481403900720352</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4125871615311323</v>
+        <v>0.2540550066420347</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2854405534113996</v>
+        <v>0.3096396970134684</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3019722850574683</v>
+        <v>0.4363052963444967</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4861383111324579</v>
+        <v>0.3820028934041343</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.513861688867542</v>
+        <v>0.6179971065958657</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5414028199032452</v>
+        <v>0.4509315523571018</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4585971800967548</v>
+        <v>0.5490684476428982</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.41219</v>
+        <v>0.25445</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.28465</v>
+        <v>0.309705</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.30316</v>
+        <v>0.435845</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.486285</v>
+        <v>0.38044</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.541165</v>
+        <v>0.450345</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.427555</v>
+        <v>0.92717</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.192175</v>
+        <v>1.28766</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.61973</v>
+        <v>2.21483</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.4455481589291255</v>
+        <v>0.2944853091927074</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.2587437238363252</v>
+        <v>0.3194496244477103</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.2957081172345494</v>
+        <v>0.3860650663595822</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.4455481589291255</v>
+        <v>0.3860650663595822</v>
       </c>
       <c r="AS5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.859573548768487</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.2957081172345494</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.03661213490275006</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.1413072274345977</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.859573548768487</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.2957081172345494</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.03661213490275006</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.1413072274345977</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="BE5" t="n">
-        <v>0.1363581431510237</v>
+        <v>0.1432338236995169</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.1275905131231279</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.1218908379481708</v>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.09080438073745314</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="BG5" t="n">
-        <v>0.0917352134398185</v>
-      </c>
-      <c r="BH5" t="inlineStr">
+      <c r="BM5" t="n">
+        <v>0.08779667383554317</v>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.08408877525335112</v>
+      </c>
+      <c r="BP5" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BI5" t="n">
-        <v>0.08849626743360582</v>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.08532770157744156</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.07442421622440269</v>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="n">
+        <v>0.06029122820212026</v>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="BO5" t="n">
-        <v>0.07433927168464961</v>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0.07378448484520353</v>
-      </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BS5" t="n">
+        <v>0.04668087725205351</v>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.03909315022247263</v>
+      </c>
+      <c r="BV5" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
       </c>
-      <c r="BS5" t="n">
-        <v>0.05267464404885631</v>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="BU5" t="n">
-        <v>0.05167714279020624</v>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
       <c r="BW5" t="n">
-        <v>0.04211824384215928</v>
+        <v>0.03893491738054509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WC2026-011</t>
+          <t>WC2026-012</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-14T23:00:00+00:00</t>
+          <t>2026-06-15T02:00:00+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1895,7 +1859,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1915,205 +1879,169 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9558969607721188</v>
+        <v>1.171024170286731</v>
       </c>
       <c r="L6" t="n">
-        <v>1.143723285665135</v>
+        <v>1.404008150033904</v>
       </c>
       <c r="M6" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.2916717217772</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.3346870553158481</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.373641222906952</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.3253288671307243</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9245167070762</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.0854832929238</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>0.3307563414801561</v>
+        <v>0.4388481049862546</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3170584111994513</v>
+        <v>0.2513964417489921</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3521852473203926</v>
+        <v>0.3097554532647532</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3620714023047004</v>
+        <v>0.5170265885414118</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4356262604828165</v>
+        <v>0.4650808077513037</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2895764524332448</v>
+        <v>0.3011675067229251</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3245893381572342</v>
+        <v>0.2882904933944152</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3858342094095209</v>
+        <v>0.4105419998826598</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3502660782628037</v>
+        <v>0.4752843446257607</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6497339217371962</v>
+        <v>0.5247156553742394</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.432798356730433</v>
+        <v>0.5330117797960632</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.567201643269567</v>
+        <v>0.4669882202039368</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.289955</v>
+        <v>0.300485</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.324925</v>
+        <v>0.287175</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.38512</v>
+        <v>0.41234</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.349065</v>
+        <v>0.47553</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.4322</v>
+        <v>0.533575</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.956885</v>
+        <v>1.17051</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.14017</v>
+        <v>1.40594</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.097055</v>
+        <v>2.57645</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.3048275213372458</v>
+        <v>0.3768918357677563</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.3259926005854558</v>
+        <v>0.2679987649894325</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.3691798780772984</v>
+        <v>0.3551093992428112</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="AR6" t="n">
-        <v>0.3691798780772984</v>
+        <v>0.3768918357677563</v>
       </c>
       <c r="AS6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>OVER_2_5</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.073812689355285</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.3502660782628037</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.02493721113207936</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.07665231601491751</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>OVER_2_5</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3.073812689355285</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.3502660782628037</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0.02493721113207936</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.07665231601491751</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="BE6" t="n">
-        <v>0.14732324003563</v>
+        <v>0.1377228474227088</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.0943969096724073</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="BG6" t="n">
-        <v>0.1358959676814354</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="BI6" t="n">
-        <v>0.1267164499212531</v>
+        <v>0.08867164624452167</v>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.08789272737607232</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="BK6" t="n">
-        <v>0.1037071718117984</v>
-      </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="n">
+        <v>0.07665485637550291</v>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0-2</t>
         </is>
       </c>
-      <c r="BM6" t="n">
-        <v>0.08012323268716874</v>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="BO6" t="n">
-        <v>0.07658955461290189</v>
+        <v>0.07505628799664431</v>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
@@ -2121,7 +2049,7 @@
         </is>
       </c>
       <c r="BQ6" t="n">
-        <v>0.06401174427325459</v>
+        <v>0.07330762869668346</v>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
@@ -2129,7 +2057,7 @@
         </is>
       </c>
       <c r="BS6" t="n">
-        <v>0.05596785959991048</v>
+        <v>0.05221310766245425</v>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
@@ -2137,15 +2065,15 @@
         </is>
       </c>
       <c r="BU6" t="n">
-        <v>0.03660586124068157</v>
+        <v>0.05146225407490145</v>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="BW6" t="n">
-        <v>0.03054626898236026</v>
+        <v>0.04113403518823786</v>
       </c>
     </row>
   </sheetData>
